--- a/25-06-26/Umer.xlsx
+++ b/25-06-26/Umer.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F025E5-18FD-41F5-915E-D12DD5096DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345B3116-7116-4289-BB36-184F4954EB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3381,7 +3381,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3409,7 +3409,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4602,7 +4602,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4630,7 +4630,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5823,7 +5823,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5851,7 +5851,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7044,7 +7044,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7072,7 +7072,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8265,7 +8265,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8293,7 +8293,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9486,7 +9486,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9514,7 +9514,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10704,7 +10704,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10732,7 +10732,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11921,7 +11921,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11949,7 +11949,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13138,7 +13138,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13166,7 +13166,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14355,7 +14355,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14383,7 +14383,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18322,7 +18322,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18350,7 +18350,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19539,7 +19539,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19567,7 +19567,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20756,7 +20756,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20784,7 +20784,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21973,7 +21973,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22001,7 +22001,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23195,7 +23195,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23223,7 +23223,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23434,7 +23434,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23487,7 +23487,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>1002.8329728</v>
+        <v>0</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23561,7 +23561,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'3'!P35</f>
-        <v>770.74004775000003</v>
+        <v>0</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23878,11 +23878,11 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>3196.16</v>
+        <v>1888.64</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -23894,23 +23894,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>255.69280000000001</v>
+        <v>151.09120000000001</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>2940.4672</v>
+        <v>1737.5488</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>662.88358399999993</v>
+        <v>398.241536</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>57.15169920000001</v>
+        <v>20.462688</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>3660.5024832000004</v>
+        <v>2156.2530240000001</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23948,11 +23948,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>4629.1400000000003</v>
+        <v>2824.5600000000004</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -23960,27 +23960,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>162.01990000000006</v>
+        <v>98.859600000000029</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>231.45700000000008</v>
+        <v>141.22800000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>4235.6630999999998</v>
+        <v>2584.4724000000001</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>931.84588200000007</v>
+        <v>568.58392800000001</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>66.126597990000008</v>
+        <v>50.79924084000001</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>5233.6355799899993</v>
+        <v>3203.8555688400002</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24138,7 +24138,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>5.05</v>
+        <v>3.45</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24149,11 +24149,11 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>10730.900000000001</v>
+        <v>7618.8</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
@@ -24161,27 +24161,27 @@
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>162.01990000000006</v>
+        <v>98.859600000000029</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>719.59780000000012</v>
+        <v>524.76720000000012</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>9849.2822999999989</v>
+        <v>6995.1732000000011</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>2214.784506</v>
+        <v>1586.880504</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>139.74433239000001</v>
+        <v>87.727964040000018</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>12203.81113839</v>
+        <v>8669.7816680399992</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>12203.811138390001</v>
+        <v>8669.781668040001</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24344,7 +24344,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>10730.900000000001</v>
+        <v>7618.8</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24365,7 +24365,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>719.59780000000012</v>
+        <v>524.76720000000012</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24386,7 +24386,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>162.01990000000006</v>
+        <v>98.859600000000029</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24408,7 +24408,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>9849.2823000000026</v>
+        <v>6995.1732000000002</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>2214.784506</v>
+        <v>1586.880504</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24455,7 +24455,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>12064.066806000003</v>
+        <v>8582.0537039999999</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24480,7 +24480,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>301.60167015000007</v>
+        <v>214.5513426</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24490,7 +24490,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>12365.668476150002</v>
+        <v>8796.6050465999997</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24662,7 +24662,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24690,7 +24690,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25328,37 +25328,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="3"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="6"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="1"/>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="2"/>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25488,36 +25486,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25567,7 +25565,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25588,7 +25586,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25609,7 +25607,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25631,7 +25629,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25656,7 +25654,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25678,7 +25676,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25703,7 +25701,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>8.7584898000000013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25713,7 +25711,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1760.4564498000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25885,7 +25883,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25913,7 +25911,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26495,12 +26493,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>12</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>871.68000000000006</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -26509,23 +26505,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>69.734400000000008</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>176.428032</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>24.459340800000003</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1002.8329728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26711,11 +26707,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>871.68000000000006</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -26724,23 +26720,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>69.734400000000008</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>801.94560000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>176.428032</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>24.459340800000003</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1002.8329728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26790,7 +26786,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>871.68000000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26811,7 +26807,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>69.734400000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26854,7 +26850,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>801.94560000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26879,7 +26875,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>176.428032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26901,7 +26897,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>978.37363200000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26926,7 +26922,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>24.459340800000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26936,7 +26932,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1002.8329728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27108,7 +27104,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27136,7 +27132,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27716,12 +27712,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>6</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -27730,23 +27724,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>88.214016000000001</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>12.229670400000002</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>501.4164864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27774,37 +27768,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>6</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27934,36 +27926,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>671.22</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>46.636200000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>616.34550000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>135.59601000000001</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>18.798537750000001</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>770.74004775000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28013,7 +28005,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>671.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28034,7 +28026,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>46.636200000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28055,7 +28047,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28077,7 +28069,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>616.34550000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28102,7 +28094,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>135.59601000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28124,7 +28116,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>751.94150999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28149,7 +28141,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>18.798537750000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28159,7 +28151,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>770.74004775000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28330,7 +28322,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28358,7 +28350,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29555,7 +29547,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29583,7 +29575,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30790,7 +30782,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30818,7 +30810,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
